--- a/src/nodes/LPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>12.911943775338422</v>
+        <v>9.4673351255281162</v>
       </c>
       <c r="B1">
-        <v>15.804395236676882</v>
+        <v>18.079457029334066</v>
       </c>
       <c r="C1">
         <v>374.58109848544609</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.680547893917623</v>
+        <v>8.3258486604333548</v>
       </c>
       <c r="B2">
-        <v>15.482798507798684</v>
+        <v>17.516634745828224</v>
       </c>
       <c r="C2">
         <v>374.58109848544609</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.568248478561859</v>
+        <v>7.3266871923518737</v>
       </c>
       <c r="B3">
-        <v>15.033666860883933</v>
+        <v>16.852853466819553</v>
       </c>
       <c r="C3">
         <v>374.58109848544609</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.4840753950052559</v>
+        <v>6.3611378054813006</v>
       </c>
       <c r="B4">
-        <v>14.55441602119048</v>
+        <v>16.165229278785588</v>
       </c>
       <c r="C4">
         <v>374.58109848544609</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>8.4228018831495479</v>
+        <v>5.4229543143557377</v>
       </c>
       <c r="B5">
-        <v>14.050643085280077</v>
+        <v>15.458192946690984</v>
       </c>
       <c r="C5">
         <v>374.58109848544609</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>7.3822031278761413</v>
+        <v>4.5094779767339572</v>
       </c>
       <c r="B6">
-        <v>13.524730505152942</v>
+        <v>14.733630463520871</v>
       </c>
       <c r="C6">
         <v>374.58109848544609</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>6.3609536503894288</v>
+        <v>3.6191247929234427</v>
       </c>
       <c r="B7">
-        <v>12.978097674978715</v>
+        <v>13.992665447902962</v>
       </c>
       <c r="C7">
         <v>374.58109848544609</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>5.3582196260282755</v>
+        <v>2.7508983094077606</v>
       </c>
       <c r="B8">
-        <v>12.411637499167815</v>
+        <v>13.23600473945219</v>
       </c>
       <c r="C8">
         <v>374.58109848544609</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.3727950180263635</v>
+        <v>1.9033572644531647</v>
       </c>
       <c r="B9">
-        <v>11.826641466924109</v>
+        <v>12.464670704864142</v>
       </c>
       <c r="C9">
         <v>374.58109848544609</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.4033956346574152</v>
+        <v>1.0749669980512961</v>
       </c>
       <c r="B10">
-        <v>11.224484759997019</v>
+        <v>11.679751963398497</v>
       </c>
       <c r="C10">
         <v>374.58109848544609</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2.4487968764604968</v>
+        <v>0.26426406531265562</v>
       </c>
       <c r="B11">
-        <v>10.606478745524782</v>
+        <v>10.882286617490651</v>
       </c>
       <c r="C11">
         <v>374.58109848544609</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.5083033726306363</v>
+        <v>-0.52958252943383333</v>
       </c>
       <c r="B12">
-        <v>9.9733680640626368</v>
+        <v>10.072864138350717</v>
       </c>
       <c r="C12">
         <v>374.58109848544609</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.58327707472139412</v>
+        <v>-1.304945200104408</v>
       </c>
       <c r="B13">
-        <v>9.32369426444497</v>
+        <v>9.2503299891119575</v>
       </c>
       <c r="C13">
         <v>374.58109848544609</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.32549446313586294</v>
+        <v>-2.0608827882995131</v>
       </c>
       <c r="B14">
-        <v>8.656613991239734</v>
+        <v>8.4140165540454248</v>
       </c>
       <c r="C14">
         <v>374.58109848544609</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.2215785988570687</v>
+        <v>-2.8016584281112467</v>
       </c>
       <c r="B15">
-        <v>7.975947363670004</v>
+        <v>7.5669479100502146</v>
       </c>
       <c r="C15">
         <v>374.58109848544609</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1082469240592783</v>
+        <v>-3.5311818011826581</v>
       </c>
       <c r="B16">
-        <v>7.2851977784570838</v>
+        <v>6.7118974106461007</v>
       </c>
       <c r="C16">
         <v>374.58109848544609</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.9832330531167384</v>
+        <v>-4.24674448686892</v>
       </c>
       <c r="B17">
-        <v>6.5819382676600231</v>
+        <v>5.8469438232074769</v>
       </c>
       <c r="C17">
         <v>374.58109848544609</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.8435889585147258</v>
+        <v>-4.9448234754528588</v>
       </c>
       <c r="B18">
-        <v>5.8630119244462175</v>
+        <v>4.9695880820069149</v>
       </c>
       <c r="C18">
         <v>374.58109848544609</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.6891780224254243</v>
+        <v>-5.6252555032157581</v>
       </c>
       <c r="B19">
-        <v>5.1282724510786446</v>
+        <v>4.0797143750550244</v>
       </c>
       <c r="C19">
         <v>374.58109848544609</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-5.5205664794427438</v>
+        <v>-6.288717242938513</v>
       </c>
       <c r="B20">
-        <v>4.3783262020941756</v>
+        <v>3.177802703796929</v>
       </c>
       <c r="C20">
         <v>374.58109848544609</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-6.3383205641605995</v>
+        <v>-6.9358853674020251</v>
       </c>
       <c r="B21">
-        <v>3.6137795320296835</v>
+        <v>2.2643330696777539</v>
       </c>
       <c r="C21">
         <v>374.58109848544609</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-7.142903032941792</v>
+        <v>-7.5673128887999361</v>
       </c>
       <c r="B22">
-        <v>2.8351279853521953</v>
+        <v>1.3396977548456981</v>
       </c>
       <c r="C22">
         <v>374.58109848544609</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-7.9343627292246879</v>
+        <v>-8.1830581769768713</v>
       </c>
       <c r="B23">
-        <v>2.042423866249349</v>
+        <v>0.40393816426126861</v>
       </c>
       <c r="C23">
         <v>374.58109848544609</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-8.7126450182165378</v>
+        <v>-8.7830559411901916</v>
       </c>
       <c r="B24">
-        <v>1.2356086688389434</v>
+        <v>-0.542992016411943</v>
       </c>
       <c r="C24">
         <v>374.58109848544609</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-9.477695265124602</v>
+        <v>-9.3672408906972677</v>
       </c>
       <c r="B25">
-        <v>0.41462388723877314</v>
+        <v>-1.5011391015103535</v>
       </c>
       <c r="C25">
         <v>374.58109848544609</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-10.22943691252609</v>
+        <v>-9.93552153634373</v>
       </c>
       <c r="B26">
-        <v>-0.42061246036777333</v>
+        <v>-2.470567989353432</v>
       </c>
       <c r="C26">
         <v>374.58109848544609</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-10.967705712478052</v>
+        <v>-10.48770159532822</v>
       </c>
       <c r="B27">
-        <v>-1.2702762595349473</v>
+        <v>-3.4514179141928993</v>
       </c>
       <c r="C27">
         <v>374.58109848544609</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-11.692315494407486</v>
+        <v>-11.023558586437643</v>
       </c>
       <c r="B28">
-        <v>-2.134566871751395</v>
+        <v>-4.4438466942635211</v>
       </c>
       <c r="C28">
         <v>374.58109848544609</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-12.403080087741397</v>
+        <v>-11.542870028458898</v>
       </c>
       <c r="B29">
-        <v>-3.0136836585057702</v>
+        <v>-5.4480121478000694</v>
       </c>
       <c r="C29">
         <v>374.58109848544609</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-13.099879643291283</v>
+        <v>-12.04549269686183</v>
       </c>
       <c r="B30">
-        <v>-3.9077549607718867</v>
+        <v>-6.46401587188668</v>
       </c>
       <c r="C30">
         <v>374.58109848544609</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-13.782859597406619</v>
+        <v>-12.531600393848038</v>
       </c>
       <c r="B31">
-        <v>-4.8166250374641963</v>
+        <v>-7.4917345790049446</v>
       </c>
       <c r="C31">
         <v>374.58109848544609</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-14.452231707821369</v>
+        <v>-13.00144617830205</v>
       </c>
       <c r="B32">
-        <v>-5.7400671269823178</v>
+        <v>-8.53098876048582</v>
       </c>
       <c r="C32">
         <v>374.58109848544609</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-15.108207732269502</v>
+        <v>-13.455283109108406</v>
       </c>
       <c r="B33">
-        <v>-6.6778544677258607</v>
+        <v>-9.5815989076602577</v>
       </c>
       <c r="C33">
         <v>374.58109848544609</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-15.750874349646143</v>
+        <v>-13.893214770982061</v>
       </c>
       <c r="B34">
-        <v>-7.629894239259845</v>
+        <v>-10.643491542158392</v>
       </c>
       <c r="C34">
         <v>374.58109848544609</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-16.379817923491046</v>
+        <v>-14.314746851959662</v>
       </c>
       <c r="B35">
-        <v>-8.5966293858108873</v>
+        <v>-11.717017306807087</v>
       </c>
       <c r="C35">
         <v>374.58109848544609</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-16.99449973850513</v>
+        <v>-14.719235565908287</v>
       </c>
       <c r="B36">
-        <v>-9.5786367927710057</v>
+        <v>-12.802632874732367</v>
       </c>
       <c r="C36">
         <v>374.58109848544609</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-17.594381079389308</v>
+        <v>-15.106037126695002</v>
       </c>
       <c r="B37">
-        <v>-10.576493345532221</v>
+        <v>-13.900794919060276</v>
       </c>
       <c r="C37">
         <v>374.58109848544609</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-18.17862712405109</v>
+        <v>-15.474153888833376</v>
       </c>
       <c r="B38">
-        <v>-11.591093016608221</v>
+        <v>-15.012211124936018</v>
       </c>
       <c r="C38">
         <v>374.58109848544609</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-18.745218623224424</v>
+        <v>-15.82117276942301</v>
       </c>
       <c r="B39">
-        <v>-12.624598126999377</v>
+        <v>-16.138593225581456</v>
       </c>
       <c r="C39">
         <v>374.58109848544609</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-19.291840220849863</v>
+        <v>-16.144326826209994</v>
       </c>
       <c r="B40">
-        <v>-13.679488084827733</v>
+        <v>-17.281903966237653</v>
       </c>
       <c r="C40">
         <v>374.58109848544609</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-19.816176560867934</v>
+        <v>-16.440849116940409</v>
       </c>
       <c r="B41">
-        <v>-14.758242298215315</v>
+        <v>-18.444106092145617</v>
       </c>
       <c r="C41">
         <v>374.58109848544609</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-19.816176560867934</v>
+        <v>-16.440849116940409</v>
       </c>
       <c r="B42">
-        <v>-14.758242298215315</v>
+        <v>-18.444106092145617</v>
       </c>
       <c r="C42">
         <v>374.58109848544609</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-19.191238466686858</v>
+        <v>-16.024103742907407</v>
       </c>
       <c r="B43">
-        <v>-13.787217868048224</v>
+        <v>-17.367184851403241</v>
       </c>
       <c r="C43">
         <v>374.58109848544609</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-18.561292670539444</v>
+        <v>-15.601373966557947</v>
       </c>
       <c r="B44">
-        <v>-12.821555955182667</v>
+        <v>-16.294508678352635</v>
       </c>
       <c r="C44">
         <v>374.58109848544609</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-17.924396656434</v>
+        <v>-15.170338404295586</v>
       </c>
       <c r="B45">
-        <v>-11.863336710491089</v>
+        <v>-15.227724258825488</v>
       </c>
       <c r="C45">
         <v>374.58109848544609</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-17.2786079083788</v>
+        <v>-14.728675672523872</v>
       </c>
       <c r="B46">
-        <v>-10.914640284845904</v>
+        <v>-14.168478278653462</v>
       </c>
       <c r="C46">
         <v>374.58109848544609</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-16.622263775594579</v>
+        <v>-14.274398837666919</v>
       </c>
       <c r="B47">
-        <v>-9.9772471343585636</v>
+        <v>-13.118180179762867</v>
       </c>
       <c r="C47">
         <v>374.58109848544609</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-15.954821068151867</v>
+        <v>-13.806858766231146</v>
       </c>
       <c r="B48">
-        <v>-9.0517389360965961</v>
+        <v>-12.077290428458531</v>
       </c>
       <c r="C48">
         <v>374.58109848544609</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-15.276016461333633</v>
+        <v>-13.325740774743544</v>
       </c>
       <c r="B49">
-        <v>-8.1383976723665548</v>
+        <v>-11.046032247139911</v>
       </c>
       <c r="C49">
         <v>374.58109848544609</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-14.585586630422846</v>
+        <v>-12.830730179731102</v>
       </c>
       <c r="B50">
-        <v>-7.2375053254749906</v>
+        <v>-10.024628858206469</v>
       </c>
       <c r="C50">
         <v>374.58109848544609</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-13.883377950225302</v>
+        <v>-12.321643392998228</v>
       </c>
       <c r="B51">
-        <v>-6.3492264055639618</v>
+        <v>-9.013210490923635</v>
       </c>
       <c r="C51">
         <v>374.58109848544609</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-13.1696755936381</v>
+        <v>-11.798821207459008</v>
       </c>
       <c r="B52">
-        <v>-5.4732555341175564</v>
+        <v>-8.0115354020207032</v>
       </c>
       <c r="C52">
         <v>374.58109848544609</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-12.444874433081164</v>
+        <v>-11.262735511304948</v>
       </c>
       <c r="B53">
-        <v>-4.6091698604553661</v>
+        <v>-7.0192688550929443</v>
       </c>
       <c r="C53">
         <v>374.58109848544609</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-11.709369340974414</v>
+        <v>-10.713858192727553</v>
       </c>
       <c r="B54">
-        <v>-3.7565465338969819</v>
+        <v>-6.0360761137356205</v>
       </c>
       <c r="C54">
         <v>374.58109848544609</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-10.963476013864289</v>
+        <v>-10.152566521611593</v>
       </c>
       <c r="B55">
-        <v>-2.9150474895568173</v>
+        <v>-5.0616895595443827</v>
       </c>
       <c r="C55">
         <v>374.58109848544609</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-10.207193444803282</v>
+        <v>-9.5788592946148867</v>
       </c>
       <c r="B56">
-        <v>-2.0846738057285608</v>
+        <v>-4.0961100461164195</v>
       </c>
       <c r="C56">
         <v>374.58109848544609</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-9.4404414509703987</v>
+        <v>-8.9926406900885247</v>
       </c>
       <c r="B57">
-        <v>-1.2655113465007157</v>
+        <v>-3.139405545049307</v>
       </c>
       <c r="C57">
         <v>374.58109848544609</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-8.6631398495446561</v>
+        <v>-8.3938148863835931</v>
       </c>
       <c r="B58">
-        <v>-0.45764597596179879</v>
+        <v>-2.1916440279406246</v>
       </c>
       <c r="C58">
         <v>374.58109848544609</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-7.8752185685456828</v>
+        <v>-7.7822981447064432</v>
       </c>
       <c r="B59">
-        <v>0.3388472690330569</v>
+        <v>-1.2528848953501279</v>
       </c>
       <c r="C59">
         <v>374.58109848544609</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-7.0766479793556449</v>
+        <v>-7.1580550576845132</v>
       </c>
       <c r="B60">
-        <v>1.1239366605621717</v>
+        <v>-0.32315326368634018</v>
       </c>
       <c r="C60">
         <v>374.58109848544609</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-6.2674085641973383</v>
+        <v>-6.5210623008005086</v>
       </c>
       <c r="B61">
-        <v>1.8976012979372388</v>
+        <v>0.597534321680034</v>
       </c>
       <c r="C61">
         <v>374.58109848544609</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-5.44748080529356</v>
+        <v>-5.8712965495371341</v>
       </c>
       <c r="B62">
-        <v>2.65982028046994</v>
+        <v>1.5091613153782806</v>
       </c>
       <c r="C62">
         <v>374.58109848544609</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-4.6169367153419545</v>
+        <v>-5.2088438619221069</v>
       </c>
       <c r="B63">
-        <v>3.4106707232401408</v>
+        <v>2.41178876312922</v>
       </c>
       <c r="C63">
         <v>374.58109848544609</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.7762144289395607</v>
+        <v>-4.5342278261631641</v>
       </c>
       <c r="B64">
-        <v>4.150621804400382</v>
+        <v>3.3057880750197643</v>
       </c>
       <c r="C64">
         <v>374.58109848544609</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.9258436111582697</v>
+        <v>-3.8480814130130554</v>
       </c>
       <c r="B65">
-        <v>4.8802407178713745</v>
+        <v>4.1916082522283515</v>
       </c>
       <c r="C65">
         <v>374.58109848544609</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.0663539270699736</v>
+        <v>-3.15103759322453</v>
       </c>
       <c r="B66">
-        <v>5.6000946575738331</v>
+        <v>5.0696982959334216</v>
       </c>
       <c r="C66">
         <v>374.58109848544609</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.1975624049170337</v>
+        <v>-2.4428777082956215</v>
       </c>
       <c r="B67">
-        <v>6.3099876874830843</v>
+        <v>5.939903099560726</v>
       </c>
       <c r="C67">
         <v>374.58109848544609</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.31643552562370203</v>
+        <v>-1.7199765827055056</v>
       </c>
       <c r="B68">
-        <v>7.0066713517929182</v>
+        <v>6.7996511255252674</v>
       </c>
       <c r="C68">
         <v>374.58109848544609</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.57939297140562762</v>
+        <v>-0.97950644126210951</v>
       </c>
       <c r="B69">
-        <v>7.687611731059004</v>
+        <v>7.6469364764169629</v>
       </c>
       <c r="C69">
         <v>374.58109848544609</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.4867697655278773</v>
+        <v>-0.22523562710722536</v>
       </c>
       <c r="B70">
-        <v>8.3561855710660371</v>
+        <v>8.4844322465361017</v>
       </c>
       <c r="C70">
         <v>374.58109848544609</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.4022572590806432</v>
+        <v>0.53872779431270945</v>
       </c>
       <c r="B71">
-        <v>9.01607403676041</v>
+        <v>9.3150525140111657</v>
       </c>
       <c r="C71">
         <v>374.58109848544609</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.32680032756288</v>
+        <v>1.3135129866665238</v>
       </c>
       <c r="B72">
-        <v>9.6662653045062488</v>
+        <v>10.137996300573015</v>
       </c>
       <c r="C72">
         <v>374.58109848544609</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.2619319470458761</v>
+        <v>2.1009519171147586</v>
       </c>
       <c r="B73">
-        <v>10.305117780861998</v>
+        <v>10.951964090548334</v>
       </c>
       <c r="C73">
         <v>374.58109848544609</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.2071550227289194</v>
+        <v>2.90045053766956</v>
       </c>
       <c r="B74">
-        <v>10.933163781745677</v>
+        <v>11.757377275044751</v>
       </c>
       <c r="C74">
         <v>374.58109848544609</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.1614574409233045</v>
+        <v>3.7107993323605397</v>
       </c>
       <c r="B75">
-        <v>11.5514871330725</v>
+        <v>12.555093830664957</v>
       </c>
       <c r="C75">
         <v>374.58109848544609</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.1237970832603379</v>
+        <v>4.5307529284355761</v>
       </c>
       <c r="B76">
-        <v>12.161203791387003</v>
+        <v>13.345997169210946</v>
       </c>
       <c r="C76">
         <v>374.58109848544609</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.09322584330195</v>
+        <v>5.3591783011255449</v>
       </c>
       <c r="B77">
-        <v>12.763329040188898</v>
+        <v>14.130891007843946</v>
       </c>
       <c r="C77">
         <v>374.58109848544609</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.0692016670125177</v>
+        <v>6.1954276743750327</v>
       </c>
       <c r="B78">
-        <v>13.358443340169313</v>
+        <v>14.910234849962775</v>
       </c>
       <c r="C78">
         <v>374.58109848544609</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.050706694902157</v>
+        <v>7.0382846657535341</v>
       </c>
       <c r="B79">
-        <v>13.947636670157214</v>
+        <v>15.68489154293022</v>
       </c>
       <c r="C79">
         <v>374.58109848544609</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.03585683284571</v>
+        <v>7.8854977081105133</v>
       </c>
       <c r="B80">
-        <v>14.532926619739977</v>
+        <v>16.456458247909783</v>
       </c>
       <c r="C80">
         <v>374.58109848544609</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.019793170554927</v>
+        <v>8.7312602110817785</v>
       </c>
       <c r="B81">
-        <v>15.119516372066796</v>
+        <v>17.229053900736826</v>
       </c>
       <c r="C81">
         <v>374.58109848544609</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>12.911943775338422</v>
+        <v>9.4673351255281162</v>
       </c>
       <c r="B82">
-        <v>15.804395236676882</v>
+        <v>18.079457029334066</v>
       </c>
       <c r="C82">
         <v>374.58109848544609</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>12.976802807059251</v>
+        <v>9.439386572986594</v>
       </c>
       <c r="B1">
-        <v>18.517605967435873</v>
+        <v>20.547435922378192</v>
       </c>
       <c r="C1">
         <v>442.41419819725974</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.495239943447077</v>
+        <v>7.9608725681274972</v>
       </c>
       <c r="B2">
-        <v>18.205014622673911</v>
+        <v>20.023320949435188</v>
       </c>
       <c r="C2">
         <v>442.41419819725974</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.239038901138514</v>
+        <v>6.7898335271514521</v>
       </c>
       <c r="B3">
-        <v>17.682053729706411</v>
+        <v>19.301953566921352</v>
       </c>
       <c r="C3">
         <v>442.41419819725974</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.02853081288086</v>
+        <v>5.6780829068020848</v>
       </c>
       <c r="B4">
-        <v>17.116439622258021</v>
+        <v>18.542551270343061</v>
       </c>
       <c r="C4">
         <v>442.41419819725974</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.8535023657958609</v>
+        <v>4.6115657723923809</v>
       </c>
       <c r="B5">
-        <v>16.517706169035751</v>
+        <v>17.75413063034518</v>
       </c>
       <c r="C5">
         <v>442.41419819725974</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.7096651089169761</v>
+        <v>3.5844092820270261</v>
       </c>
       <c r="B6">
-        <v>15.88985653032254</v>
+        <v>16.940459212911765</v>
       </c>
       <c r="C6">
         <v>442.41419819725974</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.5944979048252383</v>
+        <v>2.5931772920997069</v>
       </c>
       <c r="B7">
-        <v>15.235244123998678</v>
+        <v>16.103741384855059</v>
       </c>
       <c r="C7">
         <v>442.41419819725974</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.506446429364634</v>
+        <v>1.6357670248717164</v>
       </c>
       <c r="B8">
-        <v>14.555319872268175</v>
+        <v>15.245326127472641</v>
       </c>
       <c r="C8">
         <v>442.41419819725974</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3.4432101872710983</v>
+        <v>0.70903944211889691</v>
       </c>
       <c r="B9">
-        <v>13.852231229152089</v>
+        <v>14.367227207497352</v>
       </c>
       <c r="C9">
         <v>442.41419819725974</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.4023292496595827</v>
+        <v>-0.19036724827193025</v>
       </c>
       <c r="B10">
-        <v>13.128274475915681</v>
+        <v>13.471601293512631</v>
       </c>
       <c r="C10">
         <v>442.41419819725974</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.3814521242691549</v>
+        <v>-1.0656695934845826</v>
       </c>
       <c r="B11">
-        <v>12.385644670984023</v>
+        <v>12.560511876069038</v>
       </c>
       <c r="C11">
         <v>442.41419819725974</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.37926878613748616</v>
+        <v>-1.9186473425989197</v>
       </c>
       <c r="B12">
-        <v>11.625564689455777</v>
+        <v>11.635100705994022</v>
       </c>
       <c r="C12">
         <v>442.41419819725974</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.60147335712746208</v>
+        <v>-2.7454782972083014</v>
       </c>
       <c r="B13">
-        <v>10.845469895964234</v>
+        <v>10.692915753255463</v>
       </c>
       <c r="C13">
         <v>442.41419819725974</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.5591665437230264</v>
+        <v>-3.5439170111998175</v>
       </c>
       <c r="B14">
-        <v>10.043859485616654</v>
+        <v>9.73251651144354</v>
       </c>
       <c r="C14">
         <v>442.41419819725974</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.5008190276380335</v>
+        <v>-4.323626995121991</v>
       </c>
       <c r="B15">
-        <v>9.2272754858816235</v>
+        <v>8.7601023494972221</v>
       </c>
       <c r="C15">
         <v>442.41419819725974</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.4328582175466624</v>
+        <v>-5.0934709663789048</v>
       </c>
       <c r="B16">
-        <v>8.40171771984851</v>
+        <v>7.781358908748814</v>
       </c>
       <c r="C16">
         <v>442.41419819725974</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-4.3507721250730258</v>
+        <v>-5.8471995131354619</v>
       </c>
       <c r="B17">
-        <v>7.5629743607284921</v>
+        <v>6.7922770447551208</v>
       </c>
       <c r="C17">
         <v>442.41419819725974</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-5.2487062404098257</v>
+        <v>-6.5767104580591429</v>
       </c>
       <c r="B18">
-        <v>6.7055803720038387</v>
+        <v>5.7876590204990235</v>
       </c>
       <c r="C18">
         <v>442.41419819725974</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-6.1263753650741766</v>
+        <v>-7.281602691066893</v>
       </c>
       <c r="B19">
-        <v>5.8292695281193776</v>
+        <v>4.7672475144432456</v>
       </c>
       <c r="C19">
         <v>442.41419819725974</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-6.9848866284143094</v>
+        <v>-7.9634003688880419</v>
       </c>
       <c r="B20">
-        <v>4.9350753062605657</v>
+        <v>3.7320203089204456</v>
       </c>
       <c r="C20">
         <v>442.41419819725974</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-7.8253471597784507</v>
+        <v>-8.6236276482519081</v>
       </c>
       <c r="B21">
-        <v>4.0240311836128662</v>
+        <v>2.6829551862632917</v>
       </c>
       <c r="C21">
         <v>442.41419819725974</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-8.6486634892655623</v>
+        <v>-9.2635333352159783</v>
       </c>
       <c r="B22">
-        <v>3.0969833830469078</v>
+        <v>1.6208532848825825</v>
       </c>
       <c r="C22">
         <v>442.41419819725974</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-9.4549397499775765</v>
+        <v>-9.8832648331503812</v>
       </c>
       <c r="B23">
-        <v>2.1540291101740006</v>
+        <v>0.54580916750163366</v>
       </c>
       <c r="C23">
         <v>442.41419819725974</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-10.244079475767158</v>
+        <v>-10.4826941947534</v>
       </c>
       <c r="B24">
-        <v>1.1950783162906296</v>
+        <v>-0.54225924707810347</v>
       </c>
       <c r="C24">
         <v>442.41419819725974</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-11.015986200486976</v>
+        <v>-11.061693472723331</v>
       </c>
       <c r="B25">
-        <v>0.22004095269327095</v>
+        <v>-1.6434340400551815</v>
       </c>
       <c r="C25">
         <v>442.41419819725974</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-11.770523985522084</v>
+        <v>-11.620081980782793</v>
       </c>
       <c r="B26">
-        <v>-0.771209875869647</v>
+        <v>-2.75783112591948</v>
       </c>
       <c r="C26">
         <v>442.41419819725974</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-12.507399002387055</v>
+        <v>-12.157468076751727</v>
       </c>
       <c r="B27">
-        <v>-1.7789484508419513</v>
+        <v>-3.8857017523261996</v>
       </c>
       <c r="C27">
         <v>442.41419819725974</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-13.226277950128845</v>
+        <v>-12.673407379474405</v>
       </c>
       <c r="B28">
-        <v>-2.803485900215525</v>
+        <v>-5.0273310002218565</v>
       </c>
       <c r="C28">
         <v>442.41419819725974</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-13.926827527794405</v>
+        <v>-13.167455507795099</v>
       </c>
       <c r="B29">
-        <v>-3.8451333519822355</v>
+        <v>-6.1830039505529655</v>
       </c>
       <c r="C29">
         <v>442.41419819725974</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-14.608849658920237</v>
+        <v>-13.639356890542642</v>
       </c>
       <c r="B30">
-        <v>-4.9040757055003663</v>
+        <v>-7.3528845582272622</v>
       </c>
       <c r="C30">
         <v>442.41419819725974</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-15.272687165000997</v>
+        <v>-14.089611196484068</v>
       </c>
       <c r="B31">
-        <v>-5.979992945593728</v>
+        <v>-8.5366522739972659</v>
       </c>
       <c r="C31">
         <v>442.41419819725974</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-15.918818092020906</v>
+        <v>-14.518906904370985</v>
       </c>
       <c r="B32">
-        <v>-7.0724388284525466</v>
+        <v>-9.7338654225767325</v>
       </c>
       <c r="C32">
         <v>442.41419819725974</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-16.547720485964152</v>
+        <v>-14.927932492954984</v>
       </c>
       <c r="B33">
-        <v>-8.1809671102670247</v>
+        <v>-10.944082328679386</v>
       </c>
       <c r="C33">
         <v>442.41419819725974</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-17.159630032030798</v>
+        <v>-15.317043955168074</v>
       </c>
       <c r="B34">
-        <v>-9.30535778487656</v>
+        <v>-12.167074614479805</v>
       </c>
       <c r="C34">
         <v>442.41419819725974</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-17.75381297228428</v>
+        <v>-15.685267340663861</v>
       </c>
       <c r="B35">
-        <v>-10.446295796717234</v>
+        <v>-13.40346709199585</v>
       </c>
       <c r="C35">
         <v>442.41419819725974</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-18.329293188003867</v>
+        <v>-16.031296213276363</v>
       </c>
       <c r="B36">
-        <v>-11.604692327874293</v>
+        <v>-14.65409787070621</v>
       </c>
       <c r="C36">
         <v>442.41419819725974</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-18.88509456046884</v>
+        <v>-16.353824136839584</v>
       </c>
       <c r="B37">
-        <v>-12.781458560433007</v>
+        <v>-15.919805060089582</v>
       </c>
       <c r="C37">
         <v>442.41419819725974</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-19.419660724192333</v>
+        <v>-16.650745497719896</v>
       </c>
       <c r="B38">
-        <v>-13.978047322128012</v>
+        <v>-17.201939460736739</v>
       </c>
       <c r="C38">
         <v>442.41419819725974</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-19.929114326622816</v>
+        <v>-16.916757972413048</v>
       </c>
       <c r="B39">
-        <v>-15.198078023291435</v>
+        <v>-18.50390263768676</v>
       </c>
       <c r="C39">
         <v>442.41419819725974</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-20.408997768442642</v>
+        <v>-17.145760059947161</v>
       </c>
       <c r="B40">
-        <v>-16.445711719904789</v>
+        <v>-19.829608847090793</v>
       </c>
       <c r="C40">
         <v>442.41419819725974</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-20.854853450334126</v>
+        <v>-17.331650259350333</v>
       </c>
       <c r="B41">
-        <v>-17.725109467949576</v>
+        <v>-21.18297234509998</v>
       </c>
       <c r="C41">
         <v>442.41419819725974</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-20.854853450334126</v>
+        <v>-17.331650259350333</v>
       </c>
       <c r="B42">
-        <v>-17.725109467949576</v>
+        <v>-21.18297234509998</v>
       </c>
       <c r="C42">
         <v>442.41419819725974</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-20.21016672055136</v>
+        <v>-16.871035585081149</v>
       </c>
       <c r="B43">
-        <v>-16.631315463574271</v>
+        <v>-20.005851048898197</v>
       </c>
       <c r="C43">
         <v>442.41419819725974</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-19.565599890805903</v>
+        <v>-16.41449077850568</v>
       </c>
       <c r="B44">
-        <v>-15.537409535553092</v>
+        <v>-18.826118837000767</v>
       </c>
       <c r="C44">
         <v>442.41419819725974</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-18.917195228408907</v>
+        <v>-15.956489892615062</v>
       </c>
       <c r="B45">
-        <v>-14.447086127039093</v>
+        <v>-17.647320734176198</v>
       </c>
       <c r="C45">
         <v>442.41419819725974</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-18.260995000671503</v>
+        <v>-15.491506980400414</v>
       </c>
       <c r="B46">
-        <v>-13.364039681185323</v>
+        <v>-16.47300176519299</v>
       </c>
       <c r="C46">
         <v>442.41419819725974</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-17.593599589178517</v>
+        <v>-15.014789788635426</v>
       </c>
       <c r="B47">
-        <v>-12.291443655616224</v>
+        <v>-15.306210612089993</v>
       </c>
       <c r="C47">
         <v>442.41419819725974</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-16.913841832609435</v>
+        <v>-14.524680839223953</v>
       </c>
       <c r="B48">
-        <v>-11.230387565841818</v>
+        <v>-14.148010585987372</v>
       </c>
       <c r="C48">
         <v>442.41419819725974</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.221112683917426</v>
+        <v>-14.020296347852415</v>
       </c>
       <c r="B49">
-        <v>-10.181439941843513</v>
+        <v>-12.99896865527564</v>
       </c>
       <c r="C49">
         <v>442.41419819725974</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-15.514803096055665</v>
+        <v>-13.50075253020723</v>
       </c>
       <c r="B50">
-        <v>-9.1451693136027359</v>
+        <v>-11.85965178834531</v>
       </c>
       <c r="C50">
         <v>442.41419819725974</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-14.794525681210125</v>
+        <v>-12.965474251716476</v>
       </c>
       <c r="B51">
-        <v>-8.1219372978252213</v>
+        <v>-10.730428947529802</v>
       </c>
       <c r="C51">
         <v>442.41419819725974</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-14.060779688497973</v>
+        <v>-12.415120976774867</v>
       </c>
       <c r="B52">
-        <v>-7.1112778581139526</v>
+        <v>-9.6108770709341016</v>
       </c>
       <c r="C52">
         <v>442.41419819725974</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-13.314286026269198</v>
+        <v>-11.850660819518803</v>
       </c>
       <c r="B53">
-        <v>-6.1125180447962562</v>
+        <v>-8.5003750906061182</v>
       </c>
       <c r="C53">
         <v>442.41419819725974</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-12.555765602873773</v>
+        <v>-11.273061894084661</v>
       </c>
       <c r="B54">
-        <v>-5.1249849081994281</v>
+        <v>-7.3983019385937316</v>
       </c>
       <c r="C54">
         <v>442.41419819725974</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-11.785786987852653</v>
+        <v>-10.683083798939126</v>
       </c>
       <c r="B55">
-        <v>-4.1481477030678713</v>
+        <v>-6.304170314643418</v>
       </c>
       <c r="C55">
         <v>442.41419819725974</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-11.004309395510648</v>
+        <v>-10.080652069870029</v>
       </c>
       <c r="B56">
-        <v>-3.1820445018142793</v>
+        <v>-5.21802798929586</v>
       </c>
       <c r="C56">
         <v>442.41419819725974</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-10.211139701343553</v>
+        <v>-9.4654837269955028</v>
       </c>
       <c r="B57">
-        <v>-2.2268555812684427</v>
+        <v>-4.1400565007903234</v>
       </c>
       <c r="C57">
         <v>442.41419819725974</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-9.4060847808471539</v>
+        <v>-8.8372957904336751</v>
       </c>
       <c r="B58">
-        <v>-1.282761218260142</v>
+        <v>-3.0704373873660686</v>
       </c>
       <c r="C58">
         <v>442.41419819725974</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-8.5889753485554117</v>
+        <v>-8.1958400187122837</v>
       </c>
       <c r="B59">
-        <v>-0.34991943648123891</v>
+        <v>-2.0093299017568413</v>
       </c>
       <c r="C59">
         <v>442.41419819725974</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-7.7597374751549877</v>
+        <v>-7.5410071239975132</v>
       </c>
       <c r="B60">
-        <v>0.57160075292805912</v>
+        <v>-0.95680415467437385</v>
       </c>
       <c r="C60">
         <v>442.41419819725974</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-6.9183210703707116</v>
+        <v>-6.8727225568651527</v>
       </c>
       <c r="B61">
-        <v>1.4817525919654682</v>
+        <v>0.087092028675109151</v>
       </c>
       <c r="C61">
         <v>442.41419819725974</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.0646760439274257</v>
+        <v>-6.1909117678910031</v>
       </c>
       <c r="B62">
-        <v>2.3804893226286961</v>
+        <v>1.1223108230853787</v>
       </c>
       <c r="C62">
         <v>442.41419819725974</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.19893712488188</v>
+        <v>-5.4957573890882667</v>
       </c>
       <c r="B63">
-        <v>3.2679367110774069</v>
+        <v>2.1489693912815406</v>
       </c>
       <c r="C63">
         <v>442.41419819725974</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.3219783196185153</v>
+        <v>-4.7884707782198035</v>
       </c>
       <c r="B64">
-        <v>4.1449106201190595</v>
+        <v>3.1678448477140169</v>
       </c>
       <c r="C64">
         <v>442.41419819725974</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.43485845385369</v>
+        <v>-4.0705204744858827</v>
       </c>
       <c r="B65">
-        <v>5.0123994367230607</v>
+        <v>4.179879294764552</v>
       </c>
       <c r="C65">
         <v>442.41419819725974</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.5386363533037524</v>
+        <v>-3.3433750170867715</v>
       </c>
       <c r="B66">
-        <v>5.8713915478588232</v>
+        <v>5.1860148348149044</v>
       </c>
       <c r="C66">
         <v>442.41419819725974</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.6329655740642468</v>
+        <v>-2.6065627770388278</v>
       </c>
       <c r="B67">
-        <v>6.7215635569224279</v>
+        <v>6.1859489067970923</v>
       </c>
       <c r="C67">
         <v>442.41419819725974</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.71187859374740758</v>
+        <v>-1.8518514526227239</v>
       </c>
       <c r="B68">
-        <v>7.5573449330166866</v>
+        <v>7.1744002958442419</v>
       </c>
       <c r="C68">
         <v>442.41419819725974</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.22926864143301989</v>
+        <v>-1.0728395699013258</v>
       </c>
       <c r="B69">
-        <v>8.3744005696395014</v>
+        <v>8.147262306103924</v>
       </c>
       <c r="C69">
         <v>442.41419819725974</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.18420523237398</v>
+        <v>-0.27820963880192084</v>
       </c>
       <c r="B70">
-        <v>9.17858419216246</v>
+        <v>9.110104971580375</v>
       </c>
       <c r="C70">
         <v>442.41419819725974</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.1460947176350231</v>
+        <v>0.52257263465388648</v>
       </c>
       <c r="B71">
-        <v>9.9762774640644718</v>
+        <v>10.069000764963636</v>
       </c>
       <c r="C71">
         <v>442.41419819725974</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.1167533393154105</v>
+        <v>1.3319927439316435</v>
       </c>
       <c r="B72">
-        <v>10.765784969380027</v>
+        <v>11.022355183830289</v>
       </c>
       <c r="C72">
         <v>442.41419819725974</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.0991552748630973</v>
+        <v>2.1541339936462927</v>
       </c>
       <c r="B73">
-        <v>11.54433038884444</v>
+        <v>11.96754869238419</v>
       </c>
       <c r="C73">
         <v>442.41419819725974</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.0922537395811363</v>
+        <v>2.9875197335232047</v>
       </c>
       <c r="B74">
-        <v>12.31289086944069</v>
+        <v>12.905528596451758</v>
       </c>
       <c r="C74">
         <v>442.41419819725974</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.0939795471540608</v>
+        <v>3.8292584676949195</v>
       </c>
       <c r="B75">
-        <v>13.073397944149031</v>
+        <v>13.838149858531132</v>
       </c>
       <c r="C75">
         <v>442.41419819725974</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.1021948669372748</v>
+        <v>4.676359272812217</v>
       </c>
       <c r="B76">
-        <v>13.827847223691112</v>
+        <v>14.7673312261848</v>
       </c>
       <c r="C76">
         <v>442.41419819725974</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.1149427082871579</v>
+        <v>5.5260786270431668</v>
       </c>
       <c r="B77">
-        <v>14.578065509231204</v>
+        <v>15.694832733092332</v>
       </c>
       <c r="C77">
         <v>442.41419819725974</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.1310580848931977</v>
+        <v>6.3767620421067059</v>
       </c>
       <c r="B78">
-        <v>15.325140285962636</v>
+        <v>16.621715772337328</v>
       </c>
       <c r="C78">
         <v>442.41419819725974</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.14843071983427</v>
+        <v>7.2254464453601761</v>
       </c>
       <c r="B79">
-        <v>16.071041443904562</v>
+        <v>17.549881224600007</v>
       </c>
       <c r="C79">
         <v>442.41419819725974</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.163228144740842</v>
+        <v>8.0667840201362839</v>
       </c>
       <c r="B80">
-        <v>16.819346495142877</v>
+        <v>18.482759839851838</v>
       </c>
       <c r="C80">
         <v>442.41419819725974</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.165730179001708</v>
+        <v>8.8872876316655116</v>
       </c>
       <c r="B81">
-        <v>17.579128981912131</v>
+        <v>19.429003931757308</v>
       </c>
       <c r="C81">
         <v>442.41419819725974</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>12.976802807059251</v>
+        <v>9.439386572986594</v>
       </c>
       <c r="B82">
-        <v>18.517605967435873</v>
+        <v>20.547435922378192</v>
       </c>
       <c r="C82">
         <v>442.41419819725974</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>13.015709272530891</v>
+        <v>9.3679748286816871</v>
       </c>
       <c r="B1">
-        <v>20.773077829856309</v>
+        <v>22.653300936555993</v>
       </c>
       <c r="C1">
         <v>501.14832753435888</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.272055627944807</v>
+        <v>7.5252507586332067</v>
       </c>
       <c r="B2">
-        <v>20.487334516518033</v>
+        <v>22.181853857084075</v>
       </c>
       <c r="C2">
         <v>501.14832753435888</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9.8784140033817458</v>
+        <v>6.1833472469180926</v>
       </c>
       <c r="B3">
-        <v>19.905974806310784</v>
+        <v>21.414439102146432</v>
       </c>
       <c r="C3">
         <v>501.14832753435888</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>8.54997378126359</v>
+        <v>4.92972116099419</v>
       </c>
       <c r="B4">
-        <v>19.269546691137624</v>
+        <v>20.594855433467561</v>
       </c>
       <c r="C4">
         <v>501.14832753435888</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.2706380743797583</v>
+        <v>3.7411445893564257</v>
       </c>
       <c r="B5">
-        <v>18.59164542923477</v>
+        <v>19.736829745560271</v>
       </c>
       <c r="C5">
         <v>501.14832753435888</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.0336983043676788</v>
+        <v>2.6079846497591905</v>
       </c>
       <c r="B6">
-        <v>17.877937013911627</v>
+        <v>18.846054739570352</v>
       </c>
       <c r="C6">
         <v>501.14832753435888</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.8352395645720039</v>
+        <v>1.5246473987520934</v>
       </c>
       <c r="B7">
-        <v>17.131727933326665</v>
+        <v>17.925836243128394</v>
       </c>
       <c r="C7">
         <v>501.14832753435888</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.6728758411481648</v>
+        <v>0.48774989634245769</v>
       </c>
       <c r="B8">
-        <v>16.35503338917372</v>
+        <v>16.9781734570843</v>
       </c>
       <c r="C8">
         <v>501.14832753435888</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.5430287135183081</v>
+        <v>-0.50782716464408373</v>
       </c>
       <c r="B9">
-        <v>15.550875677080342</v>
+        <v>16.006091715400867</v>
       </c>
       <c r="C9">
         <v>501.14832753435888</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1.4418626517224082</v>
+        <v>-1.4675796884248293</v>
       </c>
       <c r="B10">
-        <v>14.722494244499771</v>
+        <v>15.012838907903531</v>
       </c>
       <c r="C10">
         <v>501.14832753435888</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.36570609500502416</v>
+        <v>-2.3967736002071378</v>
       </c>
       <c r="B11">
-        <v>13.872990052254258</v>
+        <v>14.001527014755361</v>
       </c>
       <c r="C11">
         <v>501.14832753435888</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.68746480050458059</v>
+        <v>-3.2982911784507212</v>
       </c>
       <c r="B12">
-        <v>13.004072417163416</v>
+        <v>12.97385936310932</v>
       </c>
       <c r="C12">
         <v>501.14832753435888</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.7132469803429065</v>
+        <v>-4.1657100936346581</v>
       </c>
       <c r="B13">
-        <v>12.112022566667287</v>
+        <v>11.926040577740181</v>
       </c>
       <c r="C13">
         <v>501.14832753435888</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.7090483378290533</v>
+        <v>-4.9952352671306208</v>
       </c>
       <c r="B14">
-        <v>11.194651235273627</v>
+        <v>10.855827898080019</v>
       </c>
       <c r="C14">
         <v>501.14832753435888</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.6859474557467449</v>
+        <v>-5.8028852318612865</v>
       </c>
       <c r="B15">
-        <v>10.261315275140605</v>
+        <v>9.77268772456829</v>
       </c>
       <c r="C15">
         <v>501.14832753435888</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.654104919676187</v>
+        <v>-6.6033513914121533</v>
       </c>
       <c r="B16">
-        <v>9.3205962078374025</v>
+        <v>8.6853021699820729</v>
       </c>
       <c r="C16">
         <v>501.14832753435888</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-5.6063386369189319</v>
+        <v>-7.3862030204690923</v>
       </c>
       <c r="B17">
-        <v>8.36642811492683</v>
+        <v>7.5875070354415959</v>
       </c>
       <c r="C17">
         <v>501.14832753435888</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-6.5333414379404191</v>
+        <v>-8.1379341091945765</v>
       </c>
       <c r="B18">
-        <v>7.3909502608756608</v>
+        <v>6.4713207349877448</v>
       </c>
       <c r="C18">
         <v>501.14832753435888</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.43464852414033</v>
+        <v>-8.8578596385571249</v>
       </c>
       <c r="B19">
-        <v>6.3937700817728311</v>
+        <v>5.336338446000874</v>
       </c>
       <c r="C19">
         <v>501.14832753435888</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-8.3120056896519046</v>
+        <v>-9.54849983722678</v>
       </c>
       <c r="B20">
-        <v>5.3763620566128294</v>
+        <v>4.1840495366962056</v>
       </c>
       <c r="C20">
         <v>501.14832753435888</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-9.1671587286083724</v>
+        <v>-10.212374933873576</v>
       </c>
       <c r="B21">
-        <v>4.3402006643901494</v>
+        <v>3.0159433752889688</v>
       </c>
       <c r="C21">
         <v>501.14832753435888</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-10.001538555912889</v>
+        <v>-10.851551935859892</v>
       </c>
       <c r="B22">
-        <v>3.2864944404798497</v>
+        <v>1.8332414918342572</v>
       </c>
       <c r="C22">
         <v>501.14832753435888</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-10.81531656954826</v>
+        <v>-11.466284965317483</v>
       </c>
       <c r="B23">
-        <v>2.2153881457792979</v>
+        <v>0.63609406374665056</v>
       </c>
       <c r="C23">
         <v>501.14832753435888</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-11.608349288267203</v>
+        <v>-12.056374923070434</v>
       </c>
       <c r="B24">
-        <v>1.1267605975664425</v>
+        <v>-0.57561656971939767</v>
       </c>
       <c r="C24">
         <v>501.14832753435888</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-12.380493230822438</v>
+        <v>-12.621622709942848</v>
       </c>
       <c r="B25">
-        <v>0.020490613119219202</v>
+        <v>-1.8020080693094427</v>
       </c>
       <c r="C25">
         <v>501.14832753435888</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-13.131545513735707</v>
+        <v>-13.16174612535526</v>
       </c>
       <c r="B26">
-        <v>-1.1035931607713874</v>
+        <v>-3.0432472058321611</v>
       </c>
       <c r="C26">
         <v>501.14832753435888</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-13.861065644604855</v>
+        <v>-13.676130563114024</v>
       </c>
       <c r="B27">
-        <v>-2.2458627592622471</v>
+        <v>-4.2996971903487484</v>
       </c>
       <c r="C27">
         <v>501.14832753435888</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-14.56855372879674</v>
+        <v>-14.164078315621943</v>
       </c>
       <c r="B28">
-        <v>-3.4067403879971909</v>
+        <v>-5.5717703439835358</v>
       </c>
       <c r="C28">
         <v>501.14832753435888</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-15.253509871678228</v>
+        <v>-14.624891675281821</v>
       </c>
       <c r="B29">
-        <v>-4.586648252620054</v>
+        <v>-6.8598789878608475</v>
       </c>
       <c r="C29">
         <v>501.14832753435888</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-15.915652090643446</v>
+        <v>-15.05819190484138</v>
       </c>
       <c r="B30">
-        <v>-5.7858245126143784</v>
+        <v>-8.1642469426332109</v>
       </c>
       <c r="C30">
         <v>501.14832753435888</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-16.55557005119562</v>
+        <v>-15.464876148428054</v>
       </c>
       <c r="B31">
-        <v>-7.003771142822611</v>
+        <v>-9.48434402706598</v>
       </c>
       <c r="C31">
         <v>501.14832753435888</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-17.174071330865235</v>
+        <v>-15.846160520514196</v>
       </c>
       <c r="B32">
-        <v>-8.2398060719269139</v>
+        <v>-10.819451559452718</v>
       </c>
       <c r="C32">
         <v>501.14832753435888</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-17.771963507182782</v>
+        <v>-16.20326113557217</v>
       </c>
       <c r="B33">
-        <v>-9.4932472286094587</v>
+        <v>-12.168850858086989</v>
       </c>
       <c r="C33">
         <v>501.14832753435888</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-18.349673975309187</v>
+        <v>-16.536847232483797</v>
       </c>
       <c r="B34">
-        <v>-10.763733639502798</v>
+        <v>-13.532146425873279</v>
       </c>
       <c r="C34">
         <v>501.14832753435888</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-18.906109400927107</v>
+        <v>-16.845400547768826</v>
       </c>
       <c r="B35">
-        <v>-12.052188723041084</v>
+        <v>-14.910235504159861</v>
       </c>
       <c r="C35">
         <v>501.14832753435888</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-19.439796267349642</v>
+        <v>-17.126855942356478</v>
       </c>
       <c r="B36">
-        <v>-13.359856995608874</v>
+        <v>-16.304338518905936</v>
       </c>
       <c r="C36">
         <v>501.14832753435888</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-19.949261057889885</v>
+        <v>-17.379148277175965</v>
       </c>
       <c r="B37">
-        <v>-14.687982973590724</v>
+        <v>-17.715675896070707</v>
       </c>
       <c r="C37">
         <v>501.14832753435888</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-20.432114483038355</v>
+        <v>-17.598889844599142</v>
       </c>
       <c r="B38">
-        <v>-16.038584625271909</v>
+        <v>-19.146249654012205</v>
       </c>
       <c r="C38">
         <v>501.14832753435888</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-20.882304161995251</v>
+        <v>-17.777402662768413</v>
       </c>
       <c r="B39">
-        <v>-17.416773726540555</v>
+        <v>-20.601188180683732</v>
       </c>
       <c r="C39">
         <v>501.14832753435888</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-21.2928619411382</v>
+        <v>-17.904686181268822</v>
       </c>
       <c r="B40">
-        <v>-18.828435505185542</v>
+        <v>-22.086401456437422</v>
       </c>
       <c r="C40">
         <v>501.14832753435888</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-21.656819666844825</v>
+        <v>-17.970739849685412</v>
       </c>
       <c r="B41">
-        <v>-20.279455188995733</v>
+        <v>-23.607799461625397</v>
       </c>
       <c r="C41">
         <v>501.14832753435888</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-21.656819666844825</v>
+        <v>-17.970739849685412</v>
       </c>
       <c r="B42">
-        <v>-20.279455188995733</v>
+        <v>-23.607799461625397</v>
       </c>
       <c r="C42">
         <v>501.14832753435888</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-20.977556498790893</v>
+        <v>-17.447859000278168</v>
       </c>
       <c r="B43">
-        <v>-19.094739098912861</v>
+        <v>-22.356370563331325</v>
       </c>
       <c r="C43">
         <v>501.14832753435888</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-20.30584449334453</v>
+        <v>-16.942204756179649</v>
       </c>
       <c r="B44">
-        <v>-17.903645377907267</v>
+        <v>-21.094761335486972</v>
       </c>
       <c r="C44">
         <v>501.14832753435888</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-19.635306805904964</v>
+        <v>-16.444442898721142</v>
       </c>
       <c r="B45">
-        <v>-16.71155984051228</v>
+        <v>-19.828487979365828</v>
       </c>
       <c r="C45">
         <v>501.14832753435888</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-18.959566591871397</v>
+        <v>-15.945239209233932</v>
       </c>
       <c r="B46">
-        <v>-15.523868301261194</v>
+        <v>-18.563066696241378</v>
       </c>
       <c r="C46">
         <v>501.14832753435888</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-18.273136441986022</v>
+        <v>-15.436552358541841</v>
       </c>
       <c r="B47">
-        <v>-14.345205367139354</v>
+        <v>-17.3032496342919</v>
       </c>
       <c r="C47">
         <v>501.14832753435888</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-17.574086688362812</v>
+        <v>-14.915512575438775</v>
       </c>
       <c r="B48">
-        <v>-13.177200814940079</v>
+        <v>-16.05073272931488</v>
       </c>
       <c r="C48">
         <v>501.14832753435888</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.861377098458689</v>
+        <v>-14.380542978211171</v>
       </c>
       <c r="B49">
-        <v>-12.020733213908702</v>
+        <v>-14.806447864012567</v>
       </c>
       <c r="C49">
         <v>501.14832753435888</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-16.133967439730586</v>
+        <v>-13.830066685145463</v>
       </c>
       <c r="B50">
-        <v>-10.876681133290552</v>
+        <v>-13.57132692108722</v>
       </c>
       <c r="C50">
         <v>501.14832753435888</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-15.391173138263822</v>
+        <v>-13.263026054911482</v>
       </c>
       <c r="B51">
-        <v>-9.74562275686924</v>
+        <v>-12.345994930084364</v>
       </c>
       <c r="C51">
         <v>501.14832753435888</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-14.633732254657264</v>
+        <v>-12.680440407712688</v>
       </c>
       <c r="B52">
-        <v>-8.62693472658155</v>
+        <v>-11.129849507922582</v>
       </c>
       <c r="C52">
         <v>501.14832753435888</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-13.862738508138166</v>
+        <v>-12.083848304135929</v>
       </c>
       <c r="B53">
-        <v>-7.5196932989025429</v>
+        <v>-9.9219814183637087</v>
       </c>
       <c r="C53">
         <v>501.14832753435888</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-13.079285617933785</v>
+        <v>-11.474788304768058</v>
       </c>
       <c r="B54">
-        <v>-6.4229747303072706</v>
+        <v>-8.7214814251695767</v>
       </c>
       <c r="C54">
         <v>501.14832753435888</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-12.284229198625082</v>
+        <v>-10.85445724528004</v>
       </c>
       <c r="B55">
-        <v>-5.3360563779004462</v>
+        <v>-7.5276422397403886</v>
       </c>
       <c r="C55">
         <v>501.14832753435888</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-11.477472446207878</v>
+        <v>-10.222685061679309</v>
       </c>
       <c r="B56">
-        <v>-4.259020001305414</v>
+        <v>-6.3405643640298486</v>
       </c>
       <c r="C56">
         <v>501.14832753435888</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-10.658680452031701</v>
+        <v>-9.5789599650574</v>
       </c>
       <c r="B57">
-        <v>-3.1921484607751616</v>
+        <v>-5.1605502476300185</v>
       </c>
       <c r="C57">
         <v>501.14832753435888</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-9.8275183074460681</v>
+        <v>-8.9227701665058561</v>
       </c>
       <c r="B58">
-        <v>-2.135724616562678</v>
+        <v>-3.9879023401329623</v>
       </c>
       <c r="C58">
         <v>501.14832753435888</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-8.98369210069005</v>
+        <v>-8.2536662379884174</v>
       </c>
       <c r="B59">
-        <v>-1.089996703387895</v>
+        <v>-2.8228862380062489</v>
       </c>
       <c r="C59">
         <v>501.14832753435888</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-8.1270719075608859</v>
+        <v>-7.57144819495763</v>
       </c>
       <c r="B60">
-        <v>-0.0550744538385297</v>
+        <v>-1.6656201252194798</v>
       </c>
       <c r="C60">
         <v>501.14832753435888</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-7.2575688007453447</v>
+        <v>-6.8759784137382409</v>
       </c>
       <c r="B61">
-        <v>0.96896702503076415</v>
+        <v>-0.516185332617749</v>
       </c>
       <c r="C61">
         <v>501.14832753435888</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.3750938529302061</v>
+        <v>-6.167119270655002</v>
       </c>
       <c r="B62">
-        <v>1.9820526261653282</v>
+        <v>0.62533680895383725</v>
       </c>
       <c r="C62">
         <v>501.14832753435888</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.4798544527427193</v>
+        <v>-5.4451654448210078</v>
       </c>
       <c r="B63">
-        <v>2.9843575077746793</v>
+        <v>1.7591204446869231</v>
       </c>
       <c r="C63">
         <v>501.14832753435888</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.5732432525720048</v>
+        <v>-4.712140826502746</v>
       </c>
       <c r="B64">
-        <v>3.9770578891250583</v>
+        <v>2.8863616239201519</v>
       </c>
       <c r="C64">
         <v>501.14832753435888</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.6569492207476637</v>
+        <v>-3.9705016087550544</v>
       </c>
       <c r="B65">
-        <v>4.9615802547468713</v>
+        <v>4.008511872028901</v>
       </c>
       <c r="C65">
         <v>501.14832753435888</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.7326613255992878</v>
+        <v>-3.2227039846327696</v>
       </c>
       <c r="B66">
-        <v>5.9393510891705308</v>
+        <v>5.1270227143885583</v>
       </c>
       <c r="C66">
         <v>501.14832753435888</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7998427098768695</v>
+        <v>-2.4679817339657126</v>
       </c>
       <c r="B67">
-        <v>6.90991696852257</v>
+        <v>6.2414413413073344</v>
       </c>
       <c r="C67">
         <v>501.14832753435888</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.84905321401199407</v>
+        <v>-1.692678983683664</v>
       </c>
       <c r="B68">
-        <v>7.8653048353139843</v>
+        <v>7.3436976028247294</v>
       </c>
       <c r="C68">
         <v>501.14832753435888</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.12704468258014495</v>
+        <v>-0.8861898605698687</v>
       </c>
       <c r="B69">
-        <v>8.79931749838235</v>
+        <v>8.427523793691801</v>
       </c>
       <c r="C69">
         <v>501.14832753435888</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.1184746422314689</v>
+        <v>-0.062998143721543221</v>
       </c>
       <c r="B70">
-        <v>9.7203808654870283</v>
+        <v>9.5014793277745166</v>
       </c>
       <c r="C70">
         <v>501.14832753435888</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.114360356027964</v>
+        <v>0.76110557143984225</v>
       </c>
       <c r="B71">
-        <v>10.63768095044602</v>
+        <v>10.574895902311235</v>
       </c>
       <c r="C71">
         <v>501.14832753435888</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.1175394883247129</v>
+        <v>1.5901930765097267</v>
       </c>
       <c r="B72">
-        <v>11.548821092390027</v>
+        <v>11.645367228914973</v>
       </c>
       <c r="C72">
         <v>501.14832753435888</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.132682250257921</v>
+        <v>2.4309877533619377</v>
       </c>
       <c r="B73">
-        <v>12.449856881099612</v>
+        <v>12.708920020803951</v>
       </c>
       <c r="C73">
         <v>501.14832753435888</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.1580750668191824</v>
+        <v>3.2809569579669726</v>
       </c>
       <c r="B74">
-        <v>13.342235583642108</v>
+        <v>13.767050983242603</v>
       </c>
       <c r="C74">
         <v>501.14832753435888</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.1903792052067326</v>
+        <v>4.135209820838714</v>
       </c>
       <c r="B75">
-        <v>14.228777057920977</v>
+        <v>14.822650451399341</v>
       </c>
       <c r="C75">
         <v>501.14832753435888</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.2261390875899467</v>
+        <v>4.9886785965679161</v>
       </c>
       <c r="B76">
-        <v>15.112399847897422</v>
+        <v>15.878713288012266</v>
       </c>
       <c r="C76">
         <v>501.14832753435888</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.2621816312395016</v>
+        <v>5.8367007433373574</v>
       </c>
       <c r="B77">
-        <v>15.995783905200963</v>
+        <v>16.937994894473036</v>
       </c>
       <c r="C77">
         <v>501.14832753435888</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.296580578860107</v>
+        <v>6.6764114096210347</v>
       </c>
       <c r="B78">
-        <v>16.880556126076577</v>
+        <v>18.002188299217874</v>
       </c>
       <c r="C78">
         <v>501.14832753435888</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.325906359659131</v>
+        <v>7.5027635651410387</v>
       </c>
       <c r="B79">
-        <v>17.769613089220233</v>
+        <v>19.074276123056784</v>
       </c>
       <c r="C79">
         <v>501.14832753435888</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.343989432154766</v>
+        <v>8.3067317551946172</v>
       </c>
       <c r="B80">
-        <v>18.668165523175073</v>
+        <v>20.159592098409377</v>
       </c>
       <c r="C80">
         <v>501.14832753435888</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.335316233133074</v>
+        <v>9.0657454018926469</v>
       </c>
       <c r="B81">
-        <v>19.589316016988203</v>
+        <v>21.271474658294448</v>
       </c>
       <c r="C81">
         <v>501.14832753435888</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>13.015709272530891</v>
+        <v>9.3679748286816871</v>
       </c>
       <c r="B82">
-        <v>20.773077829856309</v>
+        <v>22.653300936555993</v>
       </c>
       <c r="C82">
         <v>501.14832753435888</v>
